--- a/MAJSushiConfig/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-device-use-statement-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-device-use-statement-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -461,7 +461,7 @@
     <t>performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -566,7 +566,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -615,7 +615,7 @@
     <t>DeviceUseStatement.extension:performer.extension:actor.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-organization-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0)
 </t>
   </si>
   <si>
@@ -625,7 +625,7 @@
     <t>DeviceUseStatement.extension.url</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension</t>
   </si>
   <si>
     <t>DeviceUseStatement.extension:performer.value[x]</t>
@@ -644,7 +644,7 @@
     <t>notCovered</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-not-covered-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-not-covered-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -895,7 +895,7 @@
     <t>DeviceUseStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-condition-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-prevention-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-ald-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-work-related-accident-document|0.1.0)
+    <t xml:space="preserve">Reference(Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-prevention-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-ald-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-work-related-accident-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1299,7 +1299,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="53.76953125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
